--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 50 Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 50 Index Fund.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45B6381-296B-4793-B383-F364975BC080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF118080-FD34-4A4F-877D-196313E75B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="167">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Nifty 50 Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -109,28 +109,34 @@
     <t>Telecom - Services</t>
   </si>
   <si>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
     <t>Tata Consultancy Services Ltd.</t>
   </si>
   <si>
     <t>INE467B01029</t>
   </si>
   <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
   </si>
   <si>
     <t>State Bank Of India</t>
@@ -139,12 +145,6 @@
     <t>INE062A01020</t>
   </si>
   <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>Kotak Mahindra Bank Ltd.</t>
   </si>
   <si>
@@ -190,6 +190,15 @@
     <t>INE860A01027</t>
   </si>
   <si>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
     <t>Maruti Suzuki India Ltd.</t>
   </si>
   <si>
@@ -220,6 +229,24 @@
     <t>Consumer Durables</t>
   </si>
   <si>
+    <t>Bharat Electronics Ltd.</t>
+  </si>
+  <si>
+    <t>INE263A01024</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
     <t>Power Grid Corporation Of India Ltd.</t>
   </si>
   <si>
@@ -241,16 +268,25 @@
     <t>INE849A01020</t>
   </si>
   <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
+    <t>Bajaj Finserv Ltd.</t>
+  </si>
+  <si>
+    <t>INE918I01026</t>
+  </si>
+  <si>
+    <t>Adani Ports and Special Economic Zone Ltd.</t>
+  </si>
+  <si>
+    <t>INE742F01042</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
   </si>
   <si>
     <t>Tech Mahindra Ltd.</t>
@@ -259,19 +295,28 @@
     <t>INE669C01036</t>
   </si>
   <si>
-    <t>Bharat Electronics Ltd.</t>
-  </si>
-  <si>
-    <t>INE263A01024</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
+    <t>JSW Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE019A01038</t>
+  </si>
+  <si>
+    <t>Jio Financial Services Ltd</t>
+  </si>
+  <si>
+    <t>INE758E01017</t>
   </si>
   <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
@@ -283,28 +328,13 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>Bajaj Auto Ltd.</t>
-  </si>
-  <si>
-    <t>INE917I01010</t>
-  </si>
-  <si>
-    <t>Bajaj Finserv Ltd.</t>
-  </si>
-  <si>
-    <t>INE918I01026</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>JSW Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE019A01038</t>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
   </si>
   <si>
     <t>Coal India Ltd.</t>
@@ -316,63 +346,69 @@
     <t>Consumable Fuels</t>
   </si>
   <si>
+    <t>Shriram Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE721A01047</t>
+  </si>
+  <si>
+    <t>Nestle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE239A01024</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Cipla Ltd.</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>Tata Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE192A01025</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
     <t>Wipro Ltd.</t>
   </si>
   <si>
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Nestle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE239A01024</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Cipla Ltd.</t>
-  </si>
-  <si>
-    <t>INE059A01026</t>
-  </si>
-  <si>
-    <t>Adani Ports and Special Economic Zone Ltd.</t>
-  </si>
-  <si>
-    <t>INE742F01042</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>Shriram Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE721A01047</t>
-  </si>
-  <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
-  </si>
-  <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
     <t>Apollo Hospitals Enterprise Ltd.</t>
   </si>
   <si>
@@ -382,28 +418,19 @@
     <t>Healthcare Services</t>
   </si>
   <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Tata Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE192A01025</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
+    <t>Adani Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>INE423A01024</t>
+  </si>
+  <si>
+    <t>Metals &amp; Minerals Trading</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
   </si>
   <si>
     <t>IndusInd Bank Ltd.</t>
@@ -412,42 +439,6 @@
     <t>INE095A01012</t>
   </si>
   <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Adani Enterprises Ltd.</t>
-  </si>
-  <si>
-    <t>INE423A01024</t>
-  </si>
-  <si>
-    <t>Metals &amp; Minerals Trading</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -502,6 +493,9 @@
     <t>Name of the Instrument</t>
   </si>
   <si>
+    <t>ETERNAL LIMITED</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -511,7 +505,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -526,7 +520,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - Nifty 50 TRI</t>
+    <t xml:space="preserve">Benchmark name - Nifty 50 TRI </t>
   </si>
 </sst>
 </file>
@@ -754,7 +748,7 @@
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -831,7 +825,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -864,13 +857,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -894,7 +887,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="20802600"/>
+          <a:off x="666750" y="20993100"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -911,13 +904,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -941,7 +934,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="23660100"/>
+          <a:off x="666750" y="23850600"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1277,19 +1270,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="30" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="53.5703125" style="30" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.85546875" style="30" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.7109375" style="30" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="36" style="30" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="11" style="30" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="38.7109375" style="30" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="11.7109375" style="30" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="29.7109375" style="30" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="26.7109375" style="30" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="10" style="29" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="53.5703125" style="29" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.85546875" style="29" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.7109375" style="29" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="36" style="29" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="11" style="29" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="38.7109375" style="29" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="11.7109375" style="29" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="29.7109375" style="29" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="26.7109375" style="29" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1377,10 +1370,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="12">
-        <v>1203551.3900000001</v>
+        <v>1350875.4600000002</v>
       </c>
       <c r="H5" s="13">
-        <v>0.9992476907675002</v>
+        <v>0.99805905487689994</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>13</v>
@@ -1414,10 +1407,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="12">
-        <v>1203551.3900000001</v>
+        <v>1350875.4600000002</v>
       </c>
       <c r="H7" s="13">
-        <v>0.9992476907675002</v>
+        <v>0.99805905487689994</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>13</v>
@@ -1440,13 +1433,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="17">
-        <v>8670747</v>
+        <v>9178871</v>
       </c>
       <c r="G8" s="18">
-        <v>147294.31</v>
+        <v>178519.86</v>
       </c>
       <c r="H8" s="19">
-        <v>0.12229099675669999</v>
+        <v>0.13189473643169999</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>13</v>
@@ -1469,13 +1462,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="17">
-        <v>8045549</v>
+        <v>8516502</v>
       </c>
       <c r="G9" s="18">
-        <v>100794.64</v>
+        <v>123131.59</v>
       </c>
       <c r="H9" s="19">
-        <v>8.3684678609299998E-2</v>
+        <v>9.0972559632599995E-2</v>
       </c>
       <c r="I9" s="18" t="s">
         <v>13</v>
@@ -1498,13 +1491,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="17">
-        <v>7737769</v>
+        <v>8175005</v>
       </c>
       <c r="G10" s="18">
-        <v>97890.52</v>
+        <v>116158.65</v>
       </c>
       <c r="H10" s="19">
-        <v>8.1273535032200001E-2</v>
+        <v>8.5820785015200005E-2</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>13</v>
@@ -1527,13 +1520,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="17">
-        <v>4106237</v>
+        <v>4343542</v>
       </c>
       <c r="G11" s="18">
-        <v>77189.039999999994</v>
+        <v>67876.53</v>
       </c>
       <c r="H11" s="19">
-        <v>6.4086145895900004E-2</v>
+        <v>5.0148801563299997E-2</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>13</v>
@@ -1556,13 +1549,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="17">
-        <v>3058071</v>
+        <v>3236949</v>
       </c>
       <c r="G12" s="18">
-        <v>49733.41</v>
+        <v>60084.25</v>
       </c>
       <c r="H12" s="19">
-        <v>4.1291128496499997E-2</v>
+        <v>4.43916789843E-2</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>13</v>
@@ -1582,16 +1575,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F13" s="17">
-        <v>1165272</v>
+        <v>1416427</v>
       </c>
       <c r="G13" s="18">
-        <v>47920.65</v>
+        <v>52055.11</v>
       </c>
       <c r="H13" s="19">
-        <v>3.9786085787900001E-2</v>
+        <v>3.8459558579999997E-2</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>13</v>
@@ -1602,25 +1595,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14" s="17">
-        <v>1342308</v>
+        <v>11231657</v>
       </c>
       <c r="G14" s="18">
-        <v>47885.5</v>
+        <v>46953.94</v>
       </c>
       <c r="H14" s="19">
-        <v>3.9756902525199998E-2</v>
+        <v>3.46906923449E-2</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>13</v>
@@ -1631,25 +1624,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F15" s="17">
-        <v>10601294</v>
+        <v>1232289</v>
       </c>
       <c r="G15" s="18">
-        <v>47440.79</v>
+        <v>42679.1</v>
       </c>
       <c r="H15" s="19">
-        <v>3.9387682362100003E-2</v>
+        <v>3.1532338450400002E-2</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>13</v>
@@ -1672,13 +1665,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="17">
-        <v>4388035</v>
+        <v>3447838</v>
       </c>
       <c r="G16" s="18">
-        <v>33915.120000000003</v>
+        <v>41105.120000000003</v>
       </c>
       <c r="H16" s="19">
-        <v>2.8158004405699998E-2</v>
+        <v>3.03694444326E-2</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>13</v>
@@ -1701,13 +1694,13 @@
         <v>17</v>
       </c>
       <c r="F17" s="17">
-        <v>3251775</v>
+        <v>4635605</v>
       </c>
       <c r="G17" s="18">
-        <v>32065.75</v>
+        <v>37655.019999999997</v>
       </c>
       <c r="H17" s="19">
-        <v>2.6622566270500001E-2</v>
+        <v>2.7820428148600002E-2</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>13</v>
@@ -1730,13 +1723,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="17">
-        <v>1674325</v>
+        <v>1774130</v>
       </c>
       <c r="G18" s="18">
-        <v>31833.94</v>
+        <v>36807.879999999997</v>
       </c>
       <c r="H18" s="19">
-        <v>2.64301061819E-2</v>
+        <v>2.7194540882999999E-2</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>13</v>
@@ -1759,13 +1752,13 @@
         <v>45</v>
       </c>
       <c r="F19" s="17">
-        <v>1009486</v>
+        <v>1069190</v>
       </c>
       <c r="G19" s="18">
-        <v>30182.12</v>
+        <v>31827.65</v>
       </c>
       <c r="H19" s="19">
-        <v>2.5058683794499999E-2</v>
+        <v>2.35150280086E-2</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>13</v>
@@ -1788,13 +1781,13 @@
         <v>48</v>
       </c>
       <c r="F20" s="17">
-        <v>319115</v>
+        <v>315507</v>
       </c>
       <c r="G20" s="18">
-        <v>25162.54</v>
+        <v>28965.119999999999</v>
       </c>
       <c r="H20" s="19">
-        <v>2.0891181047799998E-2</v>
+        <v>2.1400122474399999E-2</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>13</v>
@@ -1814,16 +1807,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F21" s="17">
-        <v>1012237</v>
+        <v>1070839</v>
       </c>
       <c r="G21" s="18">
-        <v>24990.11</v>
+        <v>25146.51</v>
       </c>
       <c r="H21" s="19">
-        <v>2.0748021162199998E-2</v>
+        <v>1.85788422006E-2</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>13</v>
@@ -1846,13 +1839,13 @@
         <v>53</v>
       </c>
       <c r="F22" s="17">
-        <v>1231584</v>
+        <v>1300871</v>
       </c>
       <c r="G22" s="18">
-        <v>21478.21</v>
+        <v>21823.41</v>
       </c>
       <c r="H22" s="19">
-        <v>1.7832268669699999E-2</v>
+        <v>1.6123656549900001E-2</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>13</v>
@@ -1875,13 +1868,13 @@
         <v>25</v>
       </c>
       <c r="F23" s="17">
-        <v>1205012</v>
+        <v>1279806</v>
       </c>
       <c r="G23" s="18">
-        <v>20791.88</v>
+        <v>20945.3</v>
       </c>
       <c r="H23" s="19">
-        <v>1.7262443672399999E-2</v>
+        <v>1.54748879087E-2</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>13</v>
@@ -1901,16 +1894,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F24" s="17">
-        <v>150088</v>
+        <v>8382602</v>
       </c>
       <c r="G24" s="18">
-        <v>18476.810000000001</v>
+        <v>19976.580000000002</v>
       </c>
       <c r="H24" s="19">
-        <v>1.53403584414E-2</v>
+        <v>1.4759174435300001E-2</v>
       </c>
       <c r="I24" s="18" t="s">
         <v>13</v>
@@ -1921,25 +1914,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F25" s="17">
-        <v>5402756</v>
+        <v>158345</v>
       </c>
       <c r="G25" s="18">
-        <v>17504.93</v>
+        <v>19506.52</v>
       </c>
       <c r="H25" s="19">
-        <v>1.45334557584E-2</v>
+        <v>1.4411882880100001E-2</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>13</v>
@@ -1959,16 +1952,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F26" s="17">
-        <v>2390133</v>
+        <v>5721243</v>
       </c>
       <c r="G26" s="18">
-        <v>17115.740000000002</v>
+        <v>19103.23</v>
       </c>
       <c r="H26" s="19">
-        <v>1.4210331036E-2</v>
+        <v>1.4113922595700001E-2</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>13</v>
@@ -1979,25 +1972,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="F27" s="17">
-        <v>472009</v>
+        <v>2517986</v>
       </c>
       <c r="G27" s="18">
-        <v>16474.29</v>
+        <v>18116.91</v>
       </c>
       <c r="H27" s="19">
-        <v>1.3677767626999999E-2</v>
+        <v>1.33852058219E-2</v>
       </c>
       <c r="I27" s="18" t="s">
         <v>13</v>
@@ -2017,16 +2010,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F28" s="17">
-        <v>5168576</v>
+        <v>497623</v>
       </c>
       <c r="G28" s="18">
-        <v>15591.01</v>
+        <v>17690.5</v>
       </c>
       <c r="H28" s="19">
-        <v>1.29444250313E-2</v>
+        <v>1.3070163929300001E-2</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>13</v>
@@ -2037,25 +2030,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F29" s="17">
-        <v>130164</v>
+        <v>4321334</v>
       </c>
       <c r="G29" s="18">
-        <v>14952.52</v>
+        <v>16619.849999999999</v>
       </c>
       <c r="H29" s="19">
-        <v>1.2414319160199999E-2</v>
+        <v>1.2279142137299999E-2</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>13</v>
@@ -2066,25 +2059,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F30" s="17">
-        <v>253407</v>
+        <v>9977295</v>
       </c>
       <c r="G30" s="18">
-        <v>14579.01</v>
+        <v>16065.44</v>
       </c>
       <c r="H30" s="19">
-        <v>1.21042127467E-2</v>
+        <v>1.1869530787500001E-2</v>
       </c>
       <c r="I30" s="18" t="s">
         <v>13</v>
@@ -2095,25 +2088,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F31" s="17">
-        <v>9454857</v>
+        <v>5468553</v>
       </c>
       <c r="G31" s="18">
-        <v>12728.13</v>
+        <v>15845.13</v>
       </c>
       <c r="H31" s="19">
-        <v>1.05675209351E-2</v>
+        <v>1.17067604975E-2</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>13</v>
@@ -2133,16 +2126,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F32" s="17">
-        <v>723937</v>
+        <v>140362</v>
       </c>
       <c r="G32" s="18">
-        <v>12121.96</v>
+        <v>15734.58</v>
       </c>
       <c r="H32" s="19">
-        <v>1.00642487211E-2</v>
+        <v>1.16250835171E-2</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>13</v>
@@ -2153,25 +2146,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="F33" s="17">
-        <v>4080730</v>
+        <v>268129</v>
       </c>
       <c r="G33" s="18">
-        <v>11942.26</v>
+        <v>15131.86</v>
       </c>
       <c r="H33" s="19">
-        <v>9.9150529230999998E-3</v>
+        <v>1.11797795854E-2</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>13</v>
@@ -2191,16 +2184,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="F34" s="17">
-        <v>516061</v>
+        <v>656423</v>
       </c>
       <c r="G34" s="18">
-        <v>11873.53</v>
+        <v>13242.68</v>
       </c>
       <c r="H34" s="19">
-        <v>9.8579898891999994E-3</v>
+        <v>9.7840082792000002E-3</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>13</v>
@@ -2223,13 +2216,13 @@
         <v>86</v>
       </c>
       <c r="F35" s="17">
-        <v>4426074</v>
+        <v>890401</v>
       </c>
       <c r="G35" s="18">
-        <v>11623.31</v>
+        <v>12757.67</v>
       </c>
       <c r="H35" s="19">
-        <v>9.6502449110999998E-3</v>
+        <v>9.4256713070000001E-3</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>13</v>
@@ -2249,16 +2242,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="F36" s="17">
-        <v>126506</v>
+        <v>545761</v>
       </c>
       <c r="G36" s="18">
-        <v>11193</v>
+        <v>12329.29</v>
       </c>
       <c r="H36" s="19">
-        <v>9.2929803376999992E-3</v>
+        <v>9.1091739313000006E-3</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>13</v>
@@ -2278,16 +2271,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F37" s="17">
-        <v>623039</v>
+        <v>765305</v>
       </c>
       <c r="G37" s="18">
-        <v>10816.58</v>
+        <v>12045.14</v>
       </c>
       <c r="H37" s="19">
-        <v>8.9804578988000004E-3</v>
+        <v>8.8992371244999997E-3</v>
       </c>
       <c r="I37" s="18" t="s">
         <v>13</v>
@@ -2307,16 +2300,16 @@
         <v>13</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F38" s="17">
-        <v>424427</v>
+        <v>463108</v>
       </c>
       <c r="G38" s="18">
-        <v>10648.24</v>
+        <v>11789.8</v>
       </c>
       <c r="H38" s="19">
-        <v>8.8406937327999997E-3</v>
+        <v>8.7105858337999994E-3</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>13</v>
@@ -2336,16 +2329,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="F39" s="17">
-        <v>1094209</v>
+        <v>133794</v>
       </c>
       <c r="G39" s="18">
-        <v>10340.280000000001</v>
+        <v>11515.65</v>
       </c>
       <c r="H39" s="19">
-        <v>8.5850101604999993E-3</v>
+        <v>8.5080372658999995E-3</v>
       </c>
       <c r="I39" s="18" t="s">
         <v>13</v>
@@ -2365,16 +2358,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F40" s="17">
-        <v>2587861</v>
+        <v>1144759</v>
       </c>
       <c r="G40" s="18">
-        <v>10245.34</v>
+        <v>11373.18</v>
       </c>
       <c r="H40" s="19">
-        <v>8.5061862926000004E-3</v>
+        <v>8.4027770270999995E-3</v>
       </c>
       <c r="I40" s="18" t="s">
         <v>13</v>
@@ -2385,25 +2378,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>99</v>
-      </c>
       <c r="D41" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F41" s="17">
-        <v>3226205</v>
+        <v>3952314</v>
       </c>
       <c r="G41" s="18">
-        <v>10062.530000000001</v>
+        <v>11329.31</v>
       </c>
       <c r="H41" s="19">
-        <v>8.3544084193999998E-3</v>
+        <v>8.3703648231999994E-3</v>
       </c>
       <c r="I41" s="18" t="s">
         <v>13</v>
@@ -2414,25 +2407,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="D42" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D42" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>102</v>
-      </c>
       <c r="F42" s="17">
-        <v>1660049</v>
+        <v>4686573</v>
       </c>
       <c r="G42" s="18">
-        <v>9865.67</v>
+        <v>11219.66</v>
       </c>
       <c r="H42" s="19">
-        <v>8.1909655434999999E-3</v>
+        <v>8.2893527842999998E-3</v>
       </c>
       <c r="I42" s="18" t="s">
         <v>13</v>
@@ -2443,25 +2436,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="D43" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>105</v>
-      </c>
       <c r="F43" s="17">
-        <v>408648</v>
+        <v>1746911</v>
       </c>
       <c r="G43" s="18">
-        <v>9452.85</v>
+        <v>11066.68</v>
       </c>
       <c r="H43" s="19">
-        <v>7.8482220303000005E-3</v>
+        <v>8.1763275064000007E-3</v>
       </c>
       <c r="I43" s="18" t="s">
         <v>13</v>
@@ -2472,25 +2465,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="D44" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>53</v>
-      </c>
       <c r="F44" s="17">
-        <v>626903</v>
+        <v>2740560</v>
       </c>
       <c r="G44" s="18">
-        <v>9274.4</v>
+        <v>10888.24</v>
       </c>
       <c r="H44" s="19">
-        <v>7.7000640440000002E-3</v>
+        <v>8.0444917725000006E-3</v>
       </c>
       <c r="I44" s="18" t="s">
         <v>13</v>
@@ -2510,16 +2503,16 @@
         <v>13</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="F45" s="17">
-        <v>840957</v>
+        <v>1688740</v>
       </c>
       <c r="G45" s="18">
-        <v>9245.06</v>
+        <v>10796.96</v>
       </c>
       <c r="H45" s="19">
-        <v>7.6757045297000002E-3</v>
+        <v>7.9770519283E-3</v>
       </c>
       <c r="I45" s="18" t="s">
         <v>13</v>
@@ -2530,25 +2523,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="D46" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D46" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>48</v>
-      </c>
       <c r="F46" s="17">
-        <v>1594087</v>
+        <v>432614</v>
       </c>
       <c r="G46" s="18">
-        <v>8667.85</v>
+        <v>10366.299999999999</v>
       </c>
       <c r="H46" s="19">
-        <v>7.1964763352E-3</v>
+        <v>7.6588700342000004E-3</v>
       </c>
       <c r="I46" s="18" t="s">
         <v>13</v>
@@ -2568,16 +2561,16 @@
         <v>13</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="F47" s="17">
-        <v>695588</v>
+        <v>1291730</v>
       </c>
       <c r="G47" s="18">
-        <v>8467.74</v>
+        <v>10034.799999999999</v>
       </c>
       <c r="H47" s="19">
-        <v>7.0303351492E-3</v>
+        <v>7.4139499165000004E-3</v>
       </c>
       <c r="I47" s="18" t="s">
         <v>13</v>
@@ -2588,25 +2581,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D48" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F48" s="17">
-        <v>156866</v>
+        <v>678774</v>
       </c>
       <c r="G48" s="18">
-        <v>8148.09</v>
+        <v>9948.7900000000009</v>
       </c>
       <c r="H48" s="19">
-        <v>6.7649459627000001E-3</v>
+        <v>7.3504036741999998E-3</v>
       </c>
       <c r="I48" s="18" t="s">
         <v>13</v>
@@ -2617,25 +2610,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D49" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F49" s="17">
-        <v>115451</v>
+        <v>540760</v>
       </c>
       <c r="G49" s="18">
-        <v>7862.79</v>
+        <v>9799.65</v>
       </c>
       <c r="H49" s="19">
-        <v>6.5280758392999997E-3</v>
+        <v>7.2402154800000002E-3</v>
       </c>
       <c r="I49" s="18" t="s">
         <v>13</v>
@@ -2655,16 +2648,16 @@
         <v>13</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="F50" s="17">
-        <v>1217574</v>
+        <v>736012</v>
       </c>
       <c r="G50" s="18">
-        <v>7768.73</v>
+        <v>9208.98</v>
       </c>
       <c r="H50" s="19">
-        <v>6.4499825908E-3</v>
+        <v>6.8038143761000001E-3</v>
       </c>
       <c r="I50" s="18" t="s">
         <v>13</v>
@@ -2675,25 +2668,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C51" s="16" t="s">
-        <v>124</v>
-      </c>
       <c r="D51" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="F51" s="17">
-        <v>742099</v>
+        <v>165805</v>
       </c>
       <c r="G51" s="18">
-        <v>7603.92</v>
+        <v>8843.2099999999991</v>
       </c>
       <c r="H51" s="19">
-        <v>6.3131492048000004E-3</v>
+        <v>6.5335747639E-3</v>
       </c>
       <c r="I51" s="18" t="s">
         <v>13</v>
@@ -2704,25 +2697,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>122</v>
-      </c>
       <c r="F52" s="17">
-        <v>510257</v>
+        <v>785709</v>
       </c>
       <c r="G52" s="18">
-        <v>7570.17</v>
+        <v>8692.2999999999993</v>
       </c>
       <c r="H52" s="19">
-        <v>6.2851282911999999E-3</v>
+        <v>6.4220788515000002E-3</v>
       </c>
       <c r="I52" s="18" t="s">
         <v>13</v>
@@ -2733,25 +2726,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C53" s="16" t="s">
-        <v>129</v>
-      </c>
       <c r="D53" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F53" s="17">
-        <v>753544</v>
+        <v>3427146</v>
       </c>
       <c r="G53" s="18">
-        <v>7469.13</v>
+        <v>8556.56</v>
       </c>
       <c r="H53" s="19">
-        <v>6.2012399025999998E-3</v>
+        <v>6.3217908973999997E-3</v>
       </c>
       <c r="I53" s="18" t="s">
         <v>13</v>
@@ -2762,25 +2755,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="D54" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D54" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="16" t="s">
-        <v>105</v>
-      </c>
       <c r="F54" s="17">
-        <v>134406</v>
+        <v>121883</v>
       </c>
       <c r="G54" s="18">
-        <v>6894.56</v>
+        <v>8386.16</v>
       </c>
       <c r="H54" s="19">
-        <v>5.7242035662999997E-3</v>
+        <v>6.1958953075000002E-3</v>
       </c>
       <c r="I54" s="18" t="s">
         <v>13</v>
@@ -2803,13 +2796,13 @@
         <v>134</v>
       </c>
       <c r="F55" s="17">
-        <v>283870</v>
+        <v>314250</v>
       </c>
       <c r="G55" s="18">
-        <v>6494.38</v>
+        <v>7918.79</v>
       </c>
       <c r="H55" s="19">
-        <v>5.3919544041E-3</v>
+        <v>5.8505911885999998E-3</v>
       </c>
       <c r="I55" s="18" t="s">
         <v>13</v>
@@ -2832,13 +2825,13 @@
         <v>45</v>
       </c>
       <c r="F56" s="17">
-        <v>147828</v>
+        <v>156608</v>
       </c>
       <c r="G56" s="18">
-        <v>6414.48</v>
+        <v>6748.71</v>
       </c>
       <c r="H56" s="19">
-        <v>5.3256174855999998E-3</v>
+        <v>4.9861081377000002E-3</v>
       </c>
       <c r="I56" s="18" t="s">
         <v>13</v>
@@ -2858,16 +2851,16 @@
         <v>13</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F57" s="17">
-        <v>2208372</v>
+        <v>794579</v>
       </c>
       <c r="G57" s="18">
-        <v>5766.06</v>
+        <v>6491.31</v>
       </c>
       <c r="H57" s="19">
-        <v>4.7872672389999999E-3</v>
+        <v>4.7959348699000001E-3</v>
       </c>
       <c r="I57" s="18" t="s">
         <v>13</v>
@@ -2878,654 +2871,621 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C59" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D58" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="16" t="s">
+      <c r="H59" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F58" s="17">
-        <v>1060149</v>
-      </c>
-      <c r="G58" s="18">
-        <v>1727.51</v>
-      </c>
-      <c r="H58" s="19">
-        <v>1.4342639563E-3</v>
-      </c>
-      <c r="I58" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="10" t="s">
+      <c r="C61" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C60" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="12" t="s">
+      <c r="C65" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H65" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="H60" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="10" t="s">
+      <c r="C67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C62" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H64" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="10" t="s">
+      <c r="C69" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H66" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="10" t="s">
+      <c r="C71" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C68" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H68" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="10" t="s">
+      <c r="C73" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C70" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J70" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="10" t="s">
+      <c r="C75" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H72" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J72" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="10" t="s">
+      <c r="C77" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H74" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="10" t="s">
+      <c r="C79" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C76" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H76" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="10" t="s">
+      <c r="C81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="10" t="s">
+      <c r="C83" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C80" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="10" t="s">
+      <c r="C85" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="12">
+        <v>1496.6</v>
+      </c>
+      <c r="H85" s="13">
+        <v>1.1057238255E-3</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="C82" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" s="12">
-        <v>4652.6000000000004</v>
-      </c>
-      <c r="H86" s="13">
-        <v>3.8628178611000001E-3</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="14" t="s">
+      <c r="C87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="21">
+        <v>1130.4741393802688</v>
+      </c>
+      <c r="H87" s="22">
+        <v>8.352212950226036E-4</v>
+      </c>
+      <c r="I87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="23" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="21">
+        <v>1353502.5341393801</v>
+      </c>
+      <c r="H88" s="22">
+        <v>0.9999999999974224</v>
+      </c>
+      <c r="I88" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="C90" s="25"/>
+    </row>
+    <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="C88" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" s="21">
-        <v>-3746.4754950401839</v>
-      </c>
-      <c r="H88" s="22">
-        <v>-3.1105086314148741E-3</v>
-      </c>
-      <c r="I88" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="s">
+      <c r="C91" s="27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="C89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="21">
-        <v>1204457.51450496</v>
-      </c>
-      <c r="H89" s="22">
-        <v>0.99999999999718547</v>
-      </c>
-      <c r="I89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B91" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="C91" s="25"/>
-    </row>
-    <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B92" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C92" s="27" t="s">
-        <v>7</v>
+      <c r="C92" s="28">
+        <v>1000000</v>
       </c>
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B93" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C93" s="29">
-        <v>29995</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B95" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
-      <c r="I95" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="C93" s="28">
+        <v>21550</v>
+      </c>
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
@@ -3533,10 +3493,11 @@
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
-    </row>
-    <row r="97" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B97" s="6" t="s">
-        <v>162</v>
+      <c r="I96" s="5"/>
+    </row>
+    <row r="97" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
@@ -3547,7 +3508,7 @@
     </row>
     <row r="98" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B98" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
@@ -3558,7 +3519,7 @@
     </row>
     <row r="99" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -3567,43 +3528,54 @@
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
     </row>
-    <row r="101" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B101" s="6" t="s">
+    <row r="100" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+    </row>
+    <row r="102" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B102" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+    </row>
+    <row r="105" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B105" s="29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B120" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
-    </row>
-    <row r="104" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B104" s="30" t="s">
+    </row>
+    <row r="121" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B121" s="29" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="119" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B119" s="30" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B120" s="30" t="s">
-        <v>168</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B97:H97"/>
     <mergeCell ref="B98:H98"/>
     <mergeCell ref="B99:H99"/>
-    <mergeCell ref="B101:H101"/>
+    <mergeCell ref="B100:H100"/>
+    <mergeCell ref="B102:H102"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="B96:I96"/>
+    <mergeCell ref="B97:H97"/>
   </mergeCells>
   <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
